--- a/artfynd/A 25612-2024 artfynd.xlsx
+++ b/artfynd/A 25612-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,66 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92025639</v>
+        <v>130815057</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85534</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>241</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Shear</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>50m S om vägen, Srm</t>
+          <t>Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>683927.9755449077</v>
+        <v>683884</v>
       </c>
       <c r="R2" t="n">
-        <v>6574458.688880458</v>
+        <v>6574213</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,22 +754,451 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130815058</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92134</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Erstavik, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>683879</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6574211</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122649526</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58039</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102626</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Törnskata</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lanius collurio</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>föda åt ungar</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Erstavik, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>683901</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6574450</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Emma Karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johan Ennerfelt</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Törnskata, skogsduva, mindre hackspett Nacka 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>92025639</v>
+      </c>
+      <c r="B5" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>50m S om vägen, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>683928</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6574459</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-03-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-03-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Anders Erixon</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Anders Erixon</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>92025668</v>
+      </c>
+      <c r="B6" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>30m O om kraftledning, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>683895</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6574455</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-03-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-03-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Erixon</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Erixon</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25612-2024 artfynd.xlsx
+++ b/artfynd/A 25612-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122649526</v>
+        <v>134623273</v>
       </c>
       <c r="B4" t="n">
-        <v>58039</v>
+        <v>75340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102626</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>föda åt ungar</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Erstavik, Srm</t>
+          <t>Hästhagen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683901</v>
+        <v>683877</v>
       </c>
       <c r="R4" t="n">
-        <v>6574450</v>
+        <v>6574346</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -942,12 +937,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Grov ek.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -962,80 +972,69 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emma Karlsson</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Ennerfelt</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Törnskata, skogsduva, mindre hackspett Nacka 2024</t>
-        </is>
-      </c>
+          <t>Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>92025639</v>
+        <v>134623256</v>
       </c>
       <c r="B5" t="n">
-        <v>104628</v>
+        <v>9371</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>101254</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skeppsvarvsfluga</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lymexylon navale</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>50m S om vägen, Srm</t>
+          <t>Hästhagen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683928</v>
+        <v>683877</v>
       </c>
       <c r="R5" t="n">
-        <v>6574459</v>
+        <v>6574346</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1059,12 +1058,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gammal grov ek med exponerad ved.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,29 +1087,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Erixon</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Erixon</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>92025668</v>
+        <v>122649526</v>
       </c>
       <c r="B6" t="n">
-        <v>104628</v>
+        <v>58039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,49 +1116,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>102626</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>föda åt ungar</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>30m O om kraftledning, Srm</t>
+          <t>Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683895</v>
+        <v>683901</v>
       </c>
       <c r="R6" t="n">
-        <v>6574455</v>
+        <v>6574450</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1169,12 +1178,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,22 +1192,479 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Emma Karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johan Ennerfelt</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Törnskata, skogsduva, mindre hackspett Nacka 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134623272</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58698</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hästhagen, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>683877</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6574346</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134623314</v>
+      </c>
+      <c r="B8" t="n">
+        <v>102637</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hästhagen, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>683877</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6574346</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>92025639</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>50m S om vägen, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>683928</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6574459</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-03-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-03-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Anders Erixon</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Anders Erixon</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>92025668</v>
+      </c>
+      <c r="B10" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>30m O om kraftledning, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>683895</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6574455</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-03-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-03-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Erixon</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Erixon</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
